--- a/alloy-batch-template-v1.xlsx
+++ b/alloy-batch-template-v1.xlsx
@@ -16,11 +16,11 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01_批量任务'!$A$1:$G$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'02_目标成分上下限'!$A$1:$AJ$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'03_转炉终点与回收率'!$A$1:$AJ$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'04_合金成分库'!$A$1:$W$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'02_目标成分上下限'!$A$1:$U$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'03_转炉终点与回收率'!$A$1:$AL$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'04_合金成分库'!$A$1:$X$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'05_价格表'!$A$1:$D$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'06_填写说明与校验规则'!$A$1:$B$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'06_填写说明与校验规则'!$A$1:$B$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -567,7 +567,242 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ3"/>
+  <dimension ref="A1:U3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>适用牌号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>最小厚度mm</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>最大厚度mm</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>炼钢牌号</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>C目标</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Si目标</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Mn目标</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>P目标</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>S目标</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>V目标</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Nb目标</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Ti目标</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Als目标</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Alt目标</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Ca目标</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Cr目标</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Ni目标</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Cu目标</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Mo目标</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>B目标</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Sb目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Q235B</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Q235B-1</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
+      <c r="R2" s="2" t="n"/>
+      <c r="S2" s="2" t="n"/>
+      <c r="T2" s="2" t="n"/>
+      <c r="U2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Q355C</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Q355C-1</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
+      <c r="P3" s="2" t="n"/>
+      <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
+      <c r="T3" s="2" t="n"/>
+      <c r="U3" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:U3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AL3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -606,6 +841,8 @@
     <col width="10" customWidth="1" min="34" max="34"/>
     <col width="10" customWidth="1" min="35" max="35"/>
     <col width="10" customWidth="1" min="36" max="36"/>
+    <col width="10" customWidth="1" min="37" max="37"/>
+    <col width="10" customWidth="1" min="38" max="38"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -631,527 +868,170 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>C下限</t>
+          <t>C终点</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>C上限</t>
+          <t>Si终点</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Si下限</t>
+          <t>Mn终点</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Si上限</t>
+          <t>P终点</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Mn下限</t>
+          <t>S终点</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Mn上限</t>
+          <t>V终点</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>P下限</t>
+          <t>Nb终点</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>P上限</t>
+          <t>Ti终点</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>S下限</t>
+          <t>Als终点</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>S上限</t>
+          <t>Alt终点</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>V下限</t>
+          <t>Ca终点</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>V上限</t>
+          <t>Cr终点</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Nb下限</t>
+          <t>Ni终点</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Nb上限</t>
+          <t>Cu终点</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Ti下限</t>
+          <t>Mo终点</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Ti上限</t>
+          <t>B终点</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Als下限</t>
+          <t>Sb终点</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Als上限</t>
+          <t>C回收率</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Alt下限</t>
+          <t>Si回收率</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Alt上限</t>
+          <t>Mn回收率</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Cr下限</t>
+          <t>P回收率</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Cr上限</t>
+          <t>S回收率</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Ni下限</t>
+          <t>V回收率</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Ni上限</t>
+          <t>Nb回收率</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Cu下限</t>
+          <t>Ti回收率</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Cu上限</t>
+          <t>Als回收率</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Mo下限</t>
+          <t>Alt回收率</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Mo上限</t>
+          <t>Ca回收率</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>B下限</t>
+          <t>Cr回收率</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>B上限</t>
+          <t>Ni回收率</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Sb下限</t>
+          <t>Cu回收率</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>Sb上限</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Q235B</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Q235B-1</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O2" s="2" t="n"/>
-      <c r="P2" s="2" t="n"/>
-      <c r="Q2" s="2" t="n"/>
-      <c r="R2" s="2" t="n"/>
-      <c r="S2" s="2" t="n"/>
-      <c r="T2" s="2" t="n"/>
-      <c r="U2" s="2" t="n"/>
-      <c r="V2" s="2" t="n"/>
-      <c r="W2" s="2" t="n"/>
-      <c r="X2" s="2" t="n"/>
-      <c r="Y2" s="2" t="n"/>
-      <c r="Z2" s="2" t="n"/>
-      <c r="AA2" s="2" t="n"/>
-      <c r="AB2" s="2" t="n"/>
-      <c r="AC2" s="2" t="n"/>
-      <c r="AD2" s="2" t="n"/>
-      <c r="AE2" s="2" t="n"/>
-      <c r="AF2" s="2" t="n"/>
-      <c r="AG2" s="2" t="n"/>
-      <c r="AH2" s="2" t="n"/>
-      <c r="AI2" s="2" t="n"/>
-      <c r="AJ2" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Q355C</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Q355C-1</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="O3" s="2" t="n"/>
-      <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
-      <c r="X3" s="2" t="n"/>
-      <c r="Y3" s="2" t="n"/>
-      <c r="Z3" s="2" t="n"/>
-      <c r="AA3" s="2" t="n"/>
-      <c r="AB3" s="2" t="n"/>
-      <c r="AC3" s="2" t="n"/>
-      <c r="AD3" s="2" t="n"/>
-      <c r="AE3" s="2" t="n"/>
-      <c r="AF3" s="2" t="n"/>
-      <c r="AG3" s="2" t="n"/>
-      <c r="AH3" s="2" t="n"/>
-      <c r="AI3" s="2" t="n"/>
-      <c r="AJ3" s="2" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:AJ3"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AJ3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
-    <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="10" customWidth="1" min="25" max="25"/>
-    <col width="10" customWidth="1" min="26" max="26"/>
-    <col width="10" customWidth="1" min="27" max="27"/>
-    <col width="10" customWidth="1" min="28" max="28"/>
-    <col width="10" customWidth="1" min="29" max="29"/>
-    <col width="10" customWidth="1" min="30" max="30"/>
-    <col width="10" customWidth="1" min="31" max="31"/>
-    <col width="10" customWidth="1" min="32" max="32"/>
-    <col width="10" customWidth="1" min="33" max="33"/>
-    <col width="10" customWidth="1" min="34" max="34"/>
-    <col width="10" customWidth="1" min="35" max="35"/>
-    <col width="10" customWidth="1" min="36" max="36"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>适用牌号</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>最小厚度mm</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>最大厚度mm</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>炼钢牌号</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>C终点</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Si终点</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Mn终点</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>P终点</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>S终点</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>V终点</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Nb终点</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Ti终点</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Als终点</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Alt终点</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Cr终点</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Ni终点</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Cu终点</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Mo终点</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>B终点</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Sb终点</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>C回收率</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Si回收率</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Mn回收率</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>P回收率</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>S回收率</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>V回收率</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Nb回收率</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Ti回收率</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Als回收率</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Alt回收率</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>Cr回收率</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>Ni回收率</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>Cu回收率</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
           <t>Mo回收率</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>B回收率</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Sb回收率</t>
         </is>
@@ -1188,42 +1068,44 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
-      <c r="O2" s="2" t="n">
+      <c r="O2" s="2" t="n"/>
+      <c r="P2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="n"/>
       <c r="R2" s="2" t="n"/>
       <c r="S2" s="2" t="n"/>
       <c r="T2" s="2" t="n"/>
-      <c r="U2" s="2" t="n">
+      <c r="U2" s="2" t="n"/>
+      <c r="V2" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="V2" s="2" t="n">
+      <c r="W2" s="2" t="n">
         <v>0.75</v>
       </c>
-      <c r="W2" s="2" t="n">
+      <c r="X2" s="2" t="n">
         <v>0.98</v>
-      </c>
-      <c r="X2" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="Y2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Z2" s="2" t="n"/>
+      <c r="Z2" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="AA2" s="2" t="n"/>
       <c r="AB2" s="2" t="n"/>
       <c r="AC2" s="2" t="n"/>
       <c r="AD2" s="2" t="n"/>
-      <c r="AE2" s="2" t="n">
+      <c r="AE2" s="2" t="n"/>
+      <c r="AF2" s="2" t="n"/>
+      <c r="AG2" s="2" t="n">
         <v>0.96</v>
       </c>
-      <c r="AF2" s="2" t="n"/>
-      <c r="AG2" s="2" t="n"/>
       <c r="AH2" s="2" t="n"/>
       <c r="AI2" s="2" t="n"/>
       <c r="AJ2" s="2" t="n"/>
+      <c r="AK2" s="2" t="n"/>
+      <c r="AL2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1256,45 +1138,47 @@
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
-      <c r="O3" s="2" t="n">
+      <c r="O3" s="2" t="n"/>
+      <c r="P3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="n"/>
       <c r="R3" s="2" t="n"/>
       <c r="S3" s="2" t="n"/>
       <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n">
+      <c r="U3" s="2" t="n"/>
+      <c r="V3" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="V3" s="2" t="n">
+      <c r="W3" s="2" t="n">
         <v>0.8</v>
       </c>
-      <c r="W3" s="2" t="n">
+      <c r="X3" s="2" t="n">
         <v>0.98</v>
-      </c>
-      <c r="X3" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Z3" s="2" t="n"/>
+      <c r="Z3" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="AA3" s="2" t="n"/>
       <c r="AB3" s="2" t="n"/>
       <c r="AC3" s="2" t="n"/>
       <c r="AD3" s="2" t="n"/>
-      <c r="AE3" s="2" t="n">
+      <c r="AE3" s="2" t="n"/>
+      <c r="AF3" s="2" t="n"/>
+      <c r="AG3" s="2" t="n">
         <v>0.96</v>
       </c>
-      <c r="AF3" s="2" t="n"/>
-      <c r="AG3" s="2" t="n"/>
       <c r="AH3" s="2" t="n"/>
       <c r="AI3" s="2" t="n"/>
       <c r="AJ3" s="2" t="n"/>
+      <c r="AK3" s="2" t="n"/>
+      <c r="AL3" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ3"/>
+  <autoFilter ref="A1:AL3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1305,7 +1189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W8"/>
+  <dimension ref="A1:X8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1331,6 +1215,7 @@
     <col width="10" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
     <col width="28" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1416,35 +1301,40 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>Ca</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>Cr</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Ni</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Cu</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Sb</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -1503,7 +1393,8 @@
       <c r="T2" s="2" t="n"/>
       <c r="U2" s="2" t="n"/>
       <c r="V2" s="2" t="n"/>
-      <c r="W2" s="2" t="inlineStr"/>
+      <c r="W2" s="2" t="n"/>
+      <c r="X2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1556,7 +1447,8 @@
       <c r="T3" s="2" t="n"/>
       <c r="U3" s="2" t="n"/>
       <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="inlineStr"/>
+      <c r="W3" s="2" t="n"/>
+      <c r="X3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1609,7 +1501,8 @@
       <c r="T4" s="2" t="n"/>
       <c r="U4" s="2" t="n"/>
       <c r="V4" s="2" t="n"/>
-      <c r="W4" s="2" t="inlineStr"/>
+      <c r="W4" s="2" t="n"/>
+      <c r="X4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1662,7 +1555,8 @@
       <c r="T5" s="2" t="n"/>
       <c r="U5" s="2" t="n"/>
       <c r="V5" s="2" t="n"/>
-      <c r="W5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="n"/>
+      <c r="X5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1715,7 +1609,8 @@
       <c r="T6" s="2" t="n"/>
       <c r="U6" s="2" t="n"/>
       <c r="V6" s="2" t="n"/>
-      <c r="W6" s="2" t="inlineStr"/>
+      <c r="W6" s="2" t="n"/>
+      <c r="X6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1760,15 +1655,16 @@
       <c r="N7" s="2" t="n"/>
       <c r="O7" s="2" t="n"/>
       <c r="P7" s="2" t="n"/>
-      <c r="Q7" s="2" t="n">
+      <c r="Q7" s="2" t="n"/>
+      <c r="R7" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="R7" s="2" t="n"/>
       <c r="S7" s="2" t="n"/>
       <c r="T7" s="2" t="n"/>
       <c r="U7" s="2" t="n"/>
       <c r="V7" s="2" t="n"/>
-      <c r="W7" s="2" t="inlineStr"/>
+      <c r="W7" s="2" t="n"/>
+      <c r="X7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1813,18 +1709,19 @@
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="n"/>
       <c r="P8" s="2" t="n"/>
-      <c r="Q8" s="2" t="n">
+      <c r="Q8" s="2" t="n"/>
+      <c r="R8" s="2" t="n">
         <v>59.44</v>
       </c>
-      <c r="R8" s="2" t="n"/>
       <c r="S8" s="2" t="n"/>
       <c r="T8" s="2" t="n"/>
       <c r="U8" s="2" t="n"/>
       <c r="V8" s="2" t="n"/>
-      <c r="W8" s="2" t="inlineStr"/>
+      <c r="W8" s="2" t="n"/>
+      <c r="X8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W8"/>
+  <autoFilter ref="A1:X8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2018,7 +1915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2064,89 +1961,101 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>合金用量公式</t>
+          <t>外部单值规则</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>kg/t = (目标成分 - 转炉终点成分) / 合金品位 / 回收率 * 1000</t>
+          <t>目标成分表使用 元素目标 单值列：C/P/S 按上限控制；Si&lt;=0.05 按上限控制，Si&gt;0.05 按下限并自动加 0.02 上限余量；其他合金化元素按下限并自动加元素余量。旧的 元素下限/元素上限 上传列仍兼容。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>标准元素</t>
+          <t>合金用量公式</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>标准模板仅保留 C, Si, Mn, P, S, V, Nb, Ti, Als, Alt, Cr, Ni, Cu, Mo, B, Sb；旧模板里的 N 上传时会被忽略。</t>
+          <t>kg/t = (目标成分 - 转炉终点成分) / 合金品位 / 回收率 * 1000</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>P/S 规则</t>
+          <t>标准元素</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>P/S 通常只填写上限；转炉终点已超过上限时任务直接失败。</t>
+          <t>标准模板仅保留 C, Si, Mn, P, S, V, Nb, Ti, Als, Alt, Ca, Cr, Ni, Cu, Mo, B, Sb；旧模板里的 N 上传时会被忽略。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>投料方式</t>
+          <t>P/S 规则</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>投料方式只能填写 连续 或 整袋；连续物料袋重kg留空或填 0，整袋物料袋重kg必须大于 0。</t>
+          <t>P/S 通常只填写上限；转炉终点已超过上限时任务直接失败。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>路线序号</t>
+          <t>投料方式</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>最优路线明细中的路线序号只表示导出排序，从 1 开始，按成本贡献降序排列；它不是现场真实投料顺序。</t>
+          <t>投料方式只能填写 连续 或 整袋；连续物料袋重kg留空或填 0，整袋物料袋重kg必须大于 0。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>禁止内容</t>
+          <t>路线序号</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>业务输入区不允许合并单元格、公式、空表头、重复表头、隐藏必填列。</t>
+          <t>最优路线明细中的路线序号只表示导出排序，从 1 开始，按成本贡献降序排列；它不是现场真实投料顺序。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>禁止内容</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>业务输入区不允许合并单元格、公式、空表头、重复表头、隐藏必填列。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t>错误定位</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>系统会返回 sheet、行号、字段、错误码、原因和修正建议。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B10"/>
+  <autoFilter ref="A1:B11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/alloy-batch-template-v1.xlsx
+++ b/alloy-batch-template-v1.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'03_转炉终点与回收率'!$A$1:$AL$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'04_合金成分库'!$A$1:$X$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'05_价格表'!$A$1:$D$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'06_填写说明与校验规则'!$A$1:$B$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'06_填写说明与校验规则'!$A$1:$B$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1923,7 +1923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1974,96 +1974,108 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>目标成分表使用 元素目标 单值列：C/P/S 按上限控制；Ca 目标值始终不参与约束；Si&lt;=0.05 按上限控制，Si&gt;0.05 按下限并自动加 0.02 上限余量；其他合金化元素按下限并自动加元素余量。旧的 元素下限/元素上限 上传列仍兼容。</t>
+          <t>目标成分表使用 元素目标 单值列：C/P/S 按上限控制；Ca 目标值始终不参与约束；Si&lt;=0.05 按上限控制，Si&gt;0.05 按下限并自动加 0.02 上限余量；Ti 目标自动加 0.004 安全余量；其他合金化元素按下限并自动加元素余量。旧的 元素下限/元素上限 上传列仍兼容。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>合金用量公式</t>
+          <t>现场工艺规则</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>kg/t = (目标成分 - 转炉终点成分) / 合金品位 / 回收率 * 1000；Als/Alt 回收率固定按 0.15 计算，其他参与计算元素必须在转炉终点与回收率表填写回收率。</t>
+          <t>LP 按 C目标-0.01 控碳；Si目标&lt;=0.04 时禁用硅锰/硅铁；铝块按现场单独录入，不参与 LP 自动优化；Ni/Cu/Mo/Sb&lt;=0.02、B&lt;=0.0002 时不投对应合金；P&lt;=0.040、S&lt;=0.030 时不投磷硫铁合金。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>标准元素</t>
+          <t>合金用量公式</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>标准模板仅保留 C, Si, Mn, P, S, V, Nb, Ti, Als, Alt, Ca, Cr, Ni, Cu, Mo, B, Sb；旧模板里的 N 上传时会被忽略。</t>
+          <t>kg/t = (目标成分 - 转炉终点成分) / 合金品位 / 回收率 * 1000；26MnB5 的 Si 回收率若录成 0 会按现场确认值 0.8 修正；其他参与计算元素必须在转炉终点与回收率表填写回收率。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>P/S 规则</t>
+          <t>标准元素</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>P/S 通常只填写上限；转炉终点已超过上限时任务直接失败。</t>
+          <t>标准模板仅保留 C, Si, Mn, P, S, V, Nb, Ti, Als, Alt, Ca, Cr, Ni, Cu, Mo, B, Sb；旧模板里的 N 上传时会被忽略。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>投料方式</t>
+          <t>P/S 规则</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>投料方式只能填写 连续 或 整袋；连续物料袋重kg留空或填 0，整袋物料袋重kg必须大于 0。</t>
+          <t>P/S 通常只填写上限；转炉终点已超过上限时任务直接失败。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>路线序号</t>
+          <t>投料方式</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>最优路线明细中的路线序号只表示导出排序，从 1 开始，按成本贡献降序排列；它不是现场真实投料顺序。</t>
+          <t>投料方式只能填写 连续 或 整袋；连续物料袋重kg留空或填 0，整袋物料袋重kg必须大于 0。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>禁止内容</t>
+          <t>路线序号</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>业务输入区不允许合并单元格、公式、空表头、重复表头、隐藏必填列。</t>
+          <t>最优路线明细中的路线序号只表示导出排序，从 1 开始，按成本贡献降序排列；它不是现场真实投料顺序。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>禁止内容</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>业务输入区不允许合并单元格、公式、空表头、重复表头、隐藏必填列。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>错误定位</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>系统会返回 sheet、行号、字段、错误码、原因和修正建议。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B11"/>
+  <autoFilter ref="A1:B12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/alloy-batch-template-v1.xlsx
+++ b/alloy-batch-template-v1.xlsx
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>目标成分表使用 元素目标 单值列：C/P/S 按上限控制；Ca 目标值始终不参与约束；Si&lt;=0.05 按上限控制，Si&gt;0.05 按下限并自动加 0.02 上限余量；Ti 目标自动加 0.004 安全余量；其他合金化元素按下限并自动加元素余量。旧的 元素下限/元素上限 上传列仍兼容。</t>
+          <t>目标成分表使用 元素目标 单值列：C/P/S 按上限控制；Ca 目标值始终不参与约束；Si&lt;=0.05 按上限控制，Si&gt;0.05 按下限并自动加 0.02 上限余量；Ti 目标自动加 0.005 安全余量；其他合金化元素按下限并自动加元素余量。旧的 元素下限/元素上限 上传列仍兼容。</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>LP 按 C目标-0.01 控碳；Si目标&lt;=0.04 时禁用硅锰/硅铁；铝块按现场单独录入，不参与 LP 自动优化；Ni/Cu/Mo/Sb&lt;=0.02、B&lt;=0.0002 时不投对应合金；P&lt;=0.040、S&lt;=0.030 时不投磷硫铁合金。</t>
+          <t>LP 按 C目标-0.005 控碳；Si目标&lt;=0.04 时禁用硅锰/硅铁；铝块按现场单独录入，不参与 LP 自动优化；Ni/Cu/Mo/Sb&lt;=0.02、B&lt;=0.0002 时不投对应合金；P&lt;=0.040、S&lt;=0.030 时不投磷硫铁合金。</t>
         </is>
       </c>
     </row>

--- a/alloy-batch-template-v1.xlsx
+++ b/alloy-batch-template-v1.xlsx
@@ -13,6 +13,7 @@
     <sheet name="04_合金成分库" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="05_价格表" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="06_填写说明与校验规则" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="07_工艺规则参数" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01_批量任务'!$A$1:$G$3</definedName>
@@ -20,7 +21,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'03_转炉终点与回收率'!$A$1:$AL$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'04_合金成分库'!$A$1:$X$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'05_价格表'!$A$1:$D$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'06_填写说明与校验规则'!$A$1:$B$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'06_填写说明与校验规则'!$A$1:$B$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'07_工艺规则参数'!$A$1:$D$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1923,7 +1925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1974,7 +1976,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>目标成分表使用 元素目标 单值列：C/P/S 按上限控制；Ca 目标值始终不参与约束；Si&lt;=0.05 按上限控制，Si&gt;0.05 按下限并自动加 0.02 上限余量；Ti 目标自动加 0.005 安全余量；其他合金化元素按下限并自动加元素余量。旧的 元素下限/元素上限 上传列仍兼容。</t>
+          <t>目标成分表使用 元素目标 单值列：C/P/S 按上限控制；Ni/Cu/Mo/Sb&lt;=0.02、B&lt;=0.0002 时可留空或直接视为不投；其余元素单值目标按下限控制。旧的 元素下限/元素上限 上传列仍兼容。</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1988,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>LP 按 C目标-0.005 控碳；Si目标&lt;=0.04 时禁用硅锰/硅铁；铝块按现场单独录入，不参与 LP 自动优化；Ni/Cu/Mo/Sb&lt;=0.02、B&lt;=0.0002 时不投对应合金；P&lt;=0.040、S&lt;=0.030 时不投磷硫铁合金。</t>
+          <t>以 07_工艺规则参数 sheet 为准：当前批准规则只有 C目标-余量、Si&lt;=阈值禁硅、金属锰兜底、铝块按现场单独录入、Ti 下限+余量、Ni/Cu/Mo/Sb/B 低目标禁投、P/S 低目标禁投磷硫铁。</t>
         </is>
       </c>
     </row>
@@ -1998,7 +2000,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>kg/t = (目标成分 - 转炉终点成分) / 合金品位 / 回收率 * 1000；26MnB5 的 Si 回收率若录成 0 会按现场确认值 0.8 修正；其他参与计算元素必须在转炉终点与回收率表填写回收率。</t>
+          <t>kg/t = (目标成分 - 有效终点成分) / 合金品位 / 回收率 * 1000；当前批量链路只使用 C/Mn 终点扣减，V/Nb/Ti/Cr 等不做终点残余扣减；26MnB5 的 Si 回收率若录成 0 会按现场确认值 0.8 修正。</t>
         </is>
       </c>
     </row>
@@ -2053,29 +2055,324 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>禁止内容</t>
+          <t>规则参数</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>业务输入区不允许合并单元格、公式、空表头、重复表头、隐藏必填列。</t>
+          <t>07_工艺规则参数 是可编辑业务 sheet；修改阈值后，预检通过的批量任务会按该 sheet 中的规则求解。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>禁止内容</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>业务输入区不允许合并单元格、公式、空表头、重复表头、隐藏必填列。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>错误定位</t>
         </is>
       </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>系统会返回 sheet、行号、字段、错误码、原因和修正建议。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B13"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>规则项</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>参数键</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>规则总开关</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>是否启用现场确认的 8 条工艺规则；是/否。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>控碳余量</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>carbon_target_margin</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>C 上限按 目标值-该余量 控制。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>禁硅阈值</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>disable_silicon_alloys_si_max</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Si 目标 &lt;= 该阈值时禁用硅锰/硅铁。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>铝块单独录入</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>manual_aluminum</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>铝块不参与 LP 自动优化，由现场单独录入。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Ti 安全余量</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>ti_safety_addition</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Ti 只在下限侧加一次该余量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Ni 禁投阈值</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>trace_alloy_thresholds.Ni</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Ni 目标 &lt;= 该阈值时不投镍板。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Cu 禁投阈值</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>trace_alloy_thresholds.Cu</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Cu 目标 &lt;= 该阈值时不投铜板。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Mo 禁投阈值</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>trace_alloy_thresholds.Mo</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Mo 目标 &lt;= 该阈值时不投钼铁。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Sb 禁投阈值</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>trace_alloy_thresholds.Sb</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Sb 目标 &lt;= 该阈值时不投锑锭。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>B 禁投阈值</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>trace_alloy_thresholds.B</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>B 目标 &lt;= 该阈值时不投硼铁。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>磷铁禁投阈值</t>
+        </is>
+      </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>系统会返回 sheet、行号、字段、错误码、原因和修正建议。</t>
+          <t>phosphorus_alloy_max</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>P 目标 &lt;= 该阈值时不投磷铁。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>硫铁禁投阈值</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>sulfur_alloy_max</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>S 目标 &lt;= 该阈值时不投硫铁。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B12"/>
+  <autoFilter ref="A1:D13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/alloy-batch-template-v1.xlsx
+++ b/alloy-batch-template-v1.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'04_合金成分库'!$A$1:$X$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'05_价格表'!$A$1:$D$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'06_填写说明与校验规则'!$A$1:$B$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'07_工艺规则参数'!$A$1:$D$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'07_工艺规则参数'!$A$1:$D$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>目标成分表使用 元素目标 单值列：C/P/S 按上限控制；Ni/Cu/Mo/Sb&lt;=0.02、B&lt;=0.0002 时可留空或直接视为不投；其余元素单值目标按下限控制。旧的 元素下限/元素上限 上传列仍兼容。</t>
+          <t>目标成分表使用 元素目标 单值列：C/P/S 按上限控制；Si&lt;=0.05 时只做低杂质控制、按上限处理；Ni/Cu/Mo/Sb&lt;=0.02、B&lt;=0.0002 时可留空或直接视为不投；其余元素单值目标按下限控制。旧的 元素下限/元素上限 上传列仍兼容。</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2194,72 +2194,72 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>铝块单独录入</t>
+          <t>低硅上限语义阈值</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>manual_aluminum</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="b">
-        <v>1</v>
+          <t>single_target_si_upper_only_max</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>0.05</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>铝块不参与 LP 自动优化，由现场单独录入。</t>
+          <t>Si 目标 &lt;= 该阈值时只做低杂质控制，不要求补到目标值。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Ti 安全余量</t>
+          <t>铝块单独录入</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ti_safety_addition</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>0.005</v>
+          <t>manual_aluminum</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="b">
+        <v>1</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Ti 只在下限侧加一次该余量。</t>
+          <t>铝块不参与 LP 自动优化，由现场单独录入。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Ni 禁投阈值</t>
+          <t>Ti 安全余量</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>trace_alloy_thresholds.Ni</t>
+          <t>ti_safety_addition</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.02</v>
+        <v>0.005</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Ni 目标 &lt;= 该阈值时不投镍板。</t>
+          <t>Ti 只在下限侧加一次该余量。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Cu 禁投阈值</t>
+          <t>Ni 禁投阈值</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>trace_alloy_thresholds.Cu</t>
+          <t>trace_alloy_thresholds.Ni</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -2267,19 +2267,19 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Cu 目标 &lt;= 该阈值时不投铜板。</t>
+          <t>Ni 目标 &lt;= 该阈值时不投镍板。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Mo 禁投阈值</t>
+          <t>Cu 禁投阈值</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>trace_alloy_thresholds.Mo</t>
+          <t>trace_alloy_thresholds.Cu</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -2287,19 +2287,19 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Mo 目标 &lt;= 该阈值时不投钼铁。</t>
+          <t>Cu 目标 &lt;= 该阈值时不投铜板。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Sb 禁投阈值</t>
+          <t>Mo 禁投阈值</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>trace_alloy_thresholds.Sb</t>
+          <t>trace_alloy_thresholds.Mo</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -2307,72 +2307,92 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Sb 目标 &lt;= 该阈值时不投锑锭。</t>
+          <t>Mo 目标 &lt;= 该阈值时不投钼铁。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>B 禁投阈值</t>
+          <t>Sb 禁投阈值</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>trace_alloy_thresholds.B</t>
+          <t>trace_alloy_thresholds.Sb</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.0002</v>
+        <v>0.02</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>B 目标 &lt;= 该阈值时不投硼铁。</t>
+          <t>Sb 目标 &lt;= 该阈值时不投锑锭。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>磷铁禁投阈值</t>
+          <t>B 禁投阈值</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>phosphorus_alloy_max</t>
+          <t>trace_alloy_thresholds.B</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.04</v>
+        <v>0.0002</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>P 目标 &lt;= 该阈值时不投磷铁。</t>
+          <t>B 目标 &lt;= 该阈值时不投硼铁。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>磷铁禁投阈值</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>phosphorus_alloy_max</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>P 目标 &lt;= 该阈值时不投磷铁。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>硫铁禁投阈值</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>sulfur_alloy_max</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="C14" s="2" t="n">
         <v>0.03</v>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>S 目标 &lt;= 该阈值时不投硫铁。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D13"/>
+  <autoFilter ref="A1:D14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/alloy-batch-template-v1.xlsx
+++ b/alloy-batch-template-v1.xlsx
@@ -1976,7 +1976,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>目标成分表使用 元素目标 单值列：C/P/S 按上限控制；Si&lt;=0.05 时只做低杂质控制、按上限处理；Ni/Cu/Mo/Sb&lt;=0.02、B&lt;=0.0002 时可留空或直接视为不投；其余元素单值目标按下限控制。旧的 元素下限/元素上限 上传列仍兼容。</t>
+          <t>目标成分表使用 元素目标 单值列：C/P/S 按上限控制；Si&lt;=0.05 时只做低杂质控制、按上限处理；Ni/Cu/Mo/Sb&lt;=0.02、B&lt;=0.0002 时可留空或直接视为不投；其余元素单值目标按等值控制，即下限=上限=目标值，不额外叠加安全余量。旧的 元素下限/元素上限 上传列仍兼容。</t>
         </is>
       </c>
     </row>

--- a/alloy-batch-template-v1.xlsx
+++ b/alloy-batch-template-v1.xlsx
@@ -1976,7 +1976,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>目标成分表使用 元素目标 单值列：C/P/S 按上限控制；Si&lt;=0.05 时只做低杂质控制、按上限处理；Ni/Cu/Mo/Sb&lt;=0.02、B&lt;=0.0002 时可留空或直接视为不投；其余元素单值目标按等值控制，即下限=上限=目标值，不额外叠加安全余量。旧的 元素下限/元素上限 上传列仍兼容。</t>
+          <t>目标成分表使用 元素目标 单值列：空值或 0 表示不约束；C/P/S 按上限控制；Si&lt;=低硅阈值时只做低杂质控制、按上限处理；Ni/Cu/Mo/Sb&lt;=对应阈值、B&lt;=对应阈值时可留空或直接视为不投；其余元素单值目标按精确值控制。旧的 元素下限/元素上限 上传列仍兼容。</t>
         </is>
       </c>
     </row>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>以 07_工艺规则参数 sheet 为准：当前批准规则只有 C目标-余量、Si&lt;=阈值禁硅、金属锰兜底、铝块按现场单独录入、Ti 下限+余量、Ni/Cu/Mo/Sb/B 低目标禁投、P/S 低目标禁投磷硫铁。</t>
+          <t>以 07_工艺规则参数 sheet 为准：当前批准规则包括 C目标-余量、Si&lt;=阈值禁硅、金属锰兜底、铝块按现场单独录入、Ti 单值=目标+余量、Ti 区间下限+余量、Ni/Cu/Mo/Sb/B 低目标禁投、P/S 低目标禁投磷硫铁。</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>是否启用现场确认的 8 条工艺规则；是/否。</t>
+          <t>是否启用现场确认的 9 条工艺规则；是/否。</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Ti 只在下限侧加一次该余量。</t>
+          <t>Ti 单值目标按 目标值+该余量 精确控制；Ti 区间目标只对下限加该余量。</t>
         </is>
       </c>
     </row>

--- a/alloy-batch-template-v1.xlsx
+++ b/alloy-batch-template-v1.xlsx
@@ -16,12 +16,12 @@
     <sheet name="07_工艺规则参数" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01_批量任务'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01_批量任务'!$A$1:$H$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'02_目标成分上下限'!$A$1:$U$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'03_转炉终点与回收率'!$A$1:$AL$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'04_合金成分库'!$A$1:$X$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'05_价格表'!$A$1:$D$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'06_填写说明与校验规则'!$A$1:$B$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'04_合金成分库'!$A$1:$X$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'05_价格表'!$A$1:$D$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'06_填写说明与校验规则'!$A$1:$B$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'07_工艺规则参数'!$A$1:$D$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,7 +451,8 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -487,6 +488,11 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>手工铝块kg/t</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>备注</t>
         </is>
       </c>
@@ -518,7 +524,8 @@
           <t>Q235B-1</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>正常样例，可复制新增任务</t>
         </is>
@@ -551,14 +558,15 @@
           <t>Q355C-1</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>批量任务互不影响</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:H3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1199,7 +1207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X8"/>
+  <dimension ref="A1:X9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1225,7 +1233,7 @@
     <col width="10" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
     <col width="28" customWidth="1" min="23" max="23"/>
-    <col width="10" customWidth="1" min="24" max="24"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1730,8 +1738,66 @@
       <c r="W8" s="2" t="n"/>
       <c r="X8" s="2" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>铝块</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>铝块</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>连续</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="2" t="n"/>
+      <c r="M9" s="2" t="n"/>
+      <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="Q9" s="2" t="n"/>
+      <c r="R9" s="2" t="n"/>
+      <c r="S9" s="2" t="n"/>
+      <c r="T9" s="2" t="n"/>
+      <c r="U9" s="2" t="n"/>
+      <c r="V9" s="2" t="n"/>
+      <c r="W9" s="2" t="n"/>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>手工铝块按 01_批量任务 的手工铝块kg/t 单独计入，不参与 LP 自动优化。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:X8"/>
+  <autoFilter ref="A1:X9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1742,7 +1808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1913,8 +1979,28 @@
         <v>14956</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>铝块</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>22337</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D8"/>
+  <autoFilter ref="A1:D9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1925,7 +2011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1995,101 +2081,113 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>合金用量公式</t>
+          <t>手工铝块</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>kg/t = (目标成分 - 有效终点成分) / 合金品位 / 回收率 * 1000；当前批量链路只使用 C/Mn 终点扣减，V/Nb/Ti/Cr 等不做终点残余扣减；26MnB5 的 Si 回收率若录成 0 会按现场确认值 0.8 修正。</t>
+          <t>01_批量任务 可填写 手工铝块kg/t；该值不参与 LP 自动优化，只在批量导出时按铝块价格单独计入总合金消耗和总吨钢成本。空值或 0 表示本炉不单独计入铝块。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>标准元素</t>
+          <t>合金用量公式</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>标准模板仅保留 C, Si, Mn, P, S, V, Nb, Ti, Als, Alt, Ca, Cr, Ni, Cu, Mo, B, Sb；旧模板里的 N 上传时会被忽略。</t>
+          <t>kg/t = (目标成分 - 有效终点成分) / 合金品位 / 回收率 * 1000；当前批量链路只使用 C/Mn 终点扣减，V/Nb/Ti/Cr 等不做终点残余扣减；26MnB5 的 Si 回收率若录成 0 会按现场确认值 0.8 修正。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>P/S 规则</t>
+          <t>标准元素</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>P/S 通常只填写上限；转炉终点已超过上限时任务直接失败。</t>
+          <t>标准模板仅保留 C, Si, Mn, P, S, V, Nb, Ti, Als, Alt, Ca, Cr, Ni, Cu, Mo, B, Sb；旧模板里的 N 上传时会被忽略。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>投料方式</t>
+          <t>P/S 规则</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>投料方式只能填写 连续 或 整袋；连续物料袋重kg留空或填 0，整袋物料袋重kg必须大于 0。</t>
+          <t>P/S 通常只填写上限；转炉终点已超过上限时任务直接失败。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>路线序号</t>
+          <t>投料方式</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>最优路线明细中的路线序号只表示导出排序，从 1 开始，按成本贡献降序排列；它不是现场真实投料顺序。</t>
+          <t>投料方式只能填写 连续 或 整袋；连续物料袋重kg留空或填 0，整袋物料袋重kg必须大于 0。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>规则参数</t>
+          <t>路线序号</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>07_工艺规则参数 是可编辑业务 sheet；修改阈值后，预检通过的批量任务会按该 sheet 中的规则求解。</t>
+          <t>最优路线明细中的路线序号只表示导出排序，从 1 开始，按成本贡献降序排列；它不是现场真实投料顺序。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>禁止内容</t>
+          <t>规则参数</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>业务输入区不允许合并单元格、公式、空表头、重复表头、隐藏必填列。</t>
+          <t>07_工艺规则参数 是可编辑业务 sheet；修改阈值后，预检通过的批量任务会按该 sheet 中的规则求解。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>禁止内容</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>业务输入区不允许合并单元格、公式、空表头、重复表头、隐藏必填列。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>错误定位</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>系统会返回 sheet、行号、字段、错误码、原因和修正建议。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B13"/>
+  <autoFilter ref="A1:B14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/alloy-batch-template-v1.xlsx
+++ b/alloy-batch-template-v1.xlsx
@@ -1792,7 +1792,7 @@
       <c r="W9" s="2" t="n"/>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>手工铝块按 01_批量任务 的手工铝块kg/t 单独计入，不参与 LP 自动优化。</t>
+          <t>手工铝块按 01_批量任务 的手工铝块kg/t 单独记录，不参与 LP 自动优化，也不计入最终合金成本和消耗。</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>01_批量任务 可填写 手工铝块kg/t；该值不参与 LP 自动优化，只在批量导出时按铝块价格单独计入总合金消耗和总吨钢成本。空值或 0 表示本炉不单独计入铝块。</t>
+          <t>01_批量任务 可填写 手工铝块kg/t；该值不参与 LP 自动优化，也不计入最终合金成本和合金消耗。空值或 0 表示本炉没有手工铝块记录。</t>
         </is>
       </c>
     </row>
